--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.2.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.2.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.2.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.2.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y50"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œfond of the world said Mrs.</t>
+          <t>L209: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: personthher haggardface brightening prefer so much that you shouldnâ€™t see</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L17: isolated marker/symbol line :: 80</t>
@@ -626,7 +630,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -636,7 +640,7 @@
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€œGo on; I comprehend you..To leave Southmeadow like this! He</t>
+          <t>L343: punctuation artifact: repeated periods :: “Go on; I comprehend you..To leave Southmeadow like this! He</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr">
@@ -673,7 +677,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>625</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -696,12 +700,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œThen-pardon me-you wish him to</t>
+          <t>L317: stray/suspicious non-ASCII glyph(s): U+8FCE CJK UNIFIED IDEOGRAPH-8FCE | isolated marker/symbol line :: … 迎</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: dimly, â€œhe is very nice and warm- Very But you seem excited,</t>
+          <t>L158: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -729,7 +733,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L325: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: * Â« Allow that Iâ€”erâ€”I will not speak magnificent, unparalleled recompense,</t>
+          <t>L344: line starts with digit/letter garbage token | suspicious token(s): 6Now (letter/digit mix) :: 6Now, Adelaide," he pursued, leaning | who had thought to leave it with ma-</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -779,12 +783,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œI</t>
+          <t>L389: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: My death ， theprofersor's death (for no</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN, U+FFFD REPLACEMENT CHARACTER :: - Despite his daring to live in so mother, youâ€™re wrong,â€� she insisted, Â« I</t>
+          <t>L198: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: scholar and a precious counsellor • as</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -808,7 +812,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L344: line starts with digit/letter garbage token | suspicious token(s): 6Now (letter/digit mix) :: 6Now, Adelaide," he pursued, leaning | who had thought to leave it with ma-</t>
+          <t>L382: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aWait (odd internal casing) :: aWait, please," she murmured, We can. talk just as well for a few min-</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -826,12 +830,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>73</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -850,19 +854,19 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: on him of $500, 000 â€”â€”</t>
+          <t>L422: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Gaeta nickeringinthe vansmile which feel. Promise youâ€™ll do as I ask, Car-</t>
+          <t>L385: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: 99</t>
+          <t>L67: isolated marker/symbol line :: “I</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -879,7 +883,7 @@
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L382: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aWait (odd internal casing) :: aWait, please," she murmured, We can. talk just as well for a few min-</t>
+          <t>L421: line starts with digit/letter garbage token | suspicious token(s): 0UVDOJUbUb (letter/digit mix) :: 0UVDOJUbUb</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -921,19 +925,19 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œYes.</t>
+          <t>L522: stray/suspicious non-ASCII glyph(s): U+FF1F FULLWIDTH QUESTION MARK :: him ？</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: " If Iâ€™m not mistaken, Channing has Mrs. Courtaine turned and slipped back</t>
+          <t>L415: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: ''</t>
+          <t>L89: isolated marker/symbol line :: 99</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -950,7 +954,7 @@
       <c r="R6" s="1" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr">
         <is>
-          <t>L421: line starts with digit/letter garbage token | suspicious token(s): 0UVDOJUbUb (letter/digit mix) :: 0UVDOJUbUb</t>
+          <t>L582: line starts with punctuation glued to text :: ** If you dumped a cart-load of gold at my feet</t>
         </is>
       </c>
       <c r="T6" s="1" t="inlineStr"/>
@@ -992,19 +996,19 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L209: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L611: stray/suspicious non-ASCII glyph(s): U+5E7F CJK UNIFIED IDEOGRAPH-5E7F | isolated marker/symbol line :: 广</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œYou hope such a thing!" fell in un- Ihad just declared herself. Still, her</t>
+          <t>L435: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | symbol-only separator/garbage line :: 2. €</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: ,'</t>
+          <t>L95: isolated marker/symbol line :: ''</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -1021,7 +1025,7 @@
       <c r="R7" s="1" t="inlineStr"/>
       <c r="S7" s="1" t="inlineStr">
         <is>
-          <t>L582: line starts with punctuation glued to text :: ** If you dumped a cart-load of gold at my feet</t>
+          <t>L712: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • My son, my boy," she said, catching</t>
         </is>
       </c>
       <c r="T7" s="1" t="inlineStr"/>
@@ -1063,24 +1067,24 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L280: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œAllow that I-er-I will not speak</t>
+          <t>L826: stray/suspicious non-ASCII glyph(s): U+2248 ALMOST EQUAL TO :: Equal any Imported ≈.</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: lip. " But the lad may rebel against any : Is undesired.â€�</t>
+          <t>L442: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L138: isolated marker/symbol line :: a</t>
+          <t>L96: isolated marker/symbol line :: ,'</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L158: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1128,21 +1132,17 @@
           <t>L286: suspicious token(s): Cour1 (letter/digit mix) :: A silence ensued. Van Horne Cour1"now he will vex us no more."</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L308: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: - Then-pardon meâ€”you wish him to long where money is not only scrambled</t>
+          <t>L597: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L165: isolated marker/symbol line :: 7</t>
+          <t>L138: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1191,21 +1191,17 @@
           <t>L300: suspicious token(s): 1down (letter/digit mix) :: times at smart dinner parties in New 1down for a dance of elves. On its light</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L313: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: be â€”â€”</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L111: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: "M-yes. Andâ€”erâ€”marry here? strous, unthinkable.</t>
+          <t>L712: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • My son, my boy," she said, catching</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L177: isolated marker/symbol line :: A</t>
+          <t>L165: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1237,7 +1233,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1254,21 +1250,13 @@
           <t>L301: suspicious token(s): 1aris (letter/digit mix) :: York, or perhaps in London or 1aris as green web, where not one of myriad tiny</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L317: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦ è¿Ž</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L119: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: of your own andâ€”of Archibaldâ€™s-grand- He bristled at those two curt mono-</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L193: isolated marker/symbol line :: 10</t>
+          <t>L177: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1295,12 +1283,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1317,21 +1305,13 @@
           <t>L344: line starts with digit/letter garbage token | suspicious token(s): 6Now (letter/digit mix) :: 6Now, Adelaide," he pursued, leaning | who had thought to leave it with ma-</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L326: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L209: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L193: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1376,26 +1356,18 @@
           <t>L382: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aWait (odd internal casing) :: aWait, please," she murmured, We can. talk just as well for a few min-</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L359: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: musing. " Sheâ€™s merely transcendental</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L223: isolated marker/symbol line :: 2</t>
+          <t>L209: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L391: isolated marker/symbol line :: 1-</t>
+          <t>L385: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: • •</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1435,26 +1407,18 @@
           <t>L421: line starts with digit/letter garbage token | suspicious token(s): 0UVDOJUbUb (letter/digit mix) :: 0UVDOJUbUb</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L441: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‹</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L198: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: scholar and a precious counsellor â€¢ as</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L241: isolated marker/symbol line :: ',</t>
+          <t>L223: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L393: isolated marker/symbol line :: 2=</t>
+          <t>L391: isolated marker/symbol line :: 1-</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1494,26 +1458,18 @@
           <t>L529: suspicious token(s): 62c (letter/digit mix) :: bought in Toronto at 62c ON THE</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L515: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: here to-day. It's this: â€œWhat wrong</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L217: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: My death, the professorâ€™s death (for no</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L308: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L241: isolated marker/symbol line :: ',</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L395: isolated marker/symbol line :: 173</t>
+          <t>L393: isolated marker/symbol line :: 2=</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1553,26 +1509,18 @@
           <t>L573: suspicious token(s): I11 (letter/digit mix) :: "Well, I tell you that first day is one I11</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L518: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: "To repair?" she breathed.â€œHow'</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L222: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: hereâ€”as one might say, among his own</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L401: isolated marker/symbol line :: 2</t>
+          <t>L308: isolated marker/symbol line :: ”</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L397: isolated marker/symbol line :: t</t>
+          <t>L395: isolated marker/symbol line :: 173</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1612,26 +1560,18 @@
           <t>L621: suspicious token(s): 1F (letter/digit mix) :: 1F</t>
         </is>
       </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L519: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œBy aiding your, son'</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L258: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: A sad smile touched the ladyâ€™s lips. If a knife cutting into his flesh.</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L402: isolated marker/symbol line :: 8</t>
+          <t>L317: stray/suspicious non-ASCII glyph(s): U+8FCE CJK UNIFIED IDEOGRAPH-8FCE | isolated marker/symbol line :: … 迎</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L399: symbol-only separator/garbage line :: 401166:</t>
+          <t>L397: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1659,26 +1599,18 @@
           <t>L671: suspicious token(s): 44XR (letter/digit mix) :: 44XR</t>
         </is>
       </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L525: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œPshaw!</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L260: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: she had not already appealed to her ob-â€œIt is not only ridiculous," he per-</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L441: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‹</t>
+          <t>L326: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L401: isolated marker/symbol line :: A</t>
+          <t>L399: symbol-only separator/garbage line :: 401166:</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1706,26 +1638,18 @@
           <t>L749: suspicious token(s): isReally (odd internal casing) :: CIGAR It isReally)</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L526: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œI think that I perfectly. Her</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L267: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: cultivated and honorable women. If he â€žYour son himself would never endorse</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L442: isolated marker/symbol line :: S</t>
+          <t>L359: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L405: isolated marker/symbol line :: n</t>
+          <t>L401: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1753,26 +1677,18 @@
           <t>L753: suspicious token(s): SmoKe (odd internal casing) :: 10 Cent SmoKe</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L530: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œI have</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L278: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: has lived contentedly until now, and â€œ Good day," he said, across one shoul-</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L504: symbol-only separator/garbage line :: 60.</t>
+          <t>L401: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L407: isolated marker/symbol line :: 0</t>
+          <t>L405: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1800,26 +1716,18 @@
           <t>L756: suspicious token(s): I3PIRE (letter/digit mix) :: I3PIRE 2</t>
         </is>
       </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L583: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: now tossing them an inch or so upward, â€œ She is very probably not mad," ran</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L506: isolated marker/symbol line :: E</t>
+          <t>L402: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L415: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L407: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1847,26 +1755,18 @@
           <t>L822: suspicious token(s): female0 (letter/digit mix) :: ments of the female0</t>
         </is>
       </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L584: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œAs you please." . on the porch. He had no eye, no taste</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L509: isolated marker/symbol line :: 0</t>
+          <t>L422: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L419: isolated marker/symbol line :: 0</t>
+          <t>L415: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1894,26 +1794,18 @@
           <t>L843: suspicious token(s): uU100 (letter/digit mix) :: uU100,</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L627: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: answered. â€œCuriosity has brought me.</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L320: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: reseat my having doneâ€”is an act now a distinct qualm of remorse for churlish-</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L576: isolated marker/symbol line :: ?'</t>
+          <t>L441: isolated marker/symbol line :: 》</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L423: isolated marker/symbol line :: 01</t>
+          <t>L419: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1942,21 +1834,17 @@
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L325: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: * Â« Allow that Iâ€”erâ€”I will not speak magnificent, unparalleled recompense,</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L577: isolated marker/symbol line :: ?</t>
+          <t>L442: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L425: isolated marker/symbol line :: n</t>
+          <t>L423: isolated marker/symbol line :: 01</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1985,21 +1873,17 @@
         </is>
       </c>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€œGo on; I comprehend you..To leave Southmeadow like this! He</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L580: isolated marker/symbol line :: 1</t>
+          <t>L504: symbol-only separator/garbage line :: 60.</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L427: isolated marker/symbol line :: 00</t>
+          <t>L425: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -2024,21 +1908,17 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L348: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN, U+02DC SMALL TILDE :: here to-day. Itâ€™s this : â€˜ What wrong cation, vexation, disgust.</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L609: isolated marker/symbol line :: -</t>
+          <t>L506: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L442: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L427: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -2063,21 +1943,17 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to repair." ,Iâ€žand the low of the pastured cow, and</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L610: isolated marker/symbol line :: ,</t>
+          <t>L509: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L597: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L435: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | symbol-only separator/garbage line :: 2. €</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -2102,21 +1978,17 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L353: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œTo repair ?" she breathed. How? the slumbrous amethyst of the hills had</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L686: isolated marker/symbol line :: 66</t>
+          <t>L576: isolated marker/symbol line :: ?'</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L633: isolated marker/symbol line :: /</t>
+          <t>L442: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -2141,21 +2013,17 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L354: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ By aiding your son. , , neither answer for his</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L701: isolated marker/symbol line :: P</t>
+          <t>L577: isolated marker/symbol line :: ?</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L656: isolated marker/symbol line :: 1</t>
+          <t>L597: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2180,21 +2048,17 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L356: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: "Aiding him? He needs no oneâ€™sing spirit nor blame for his</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L707: isolated marker/symbol line :: 1</t>
+          <t>L580: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L668: isolated marker/symbol line :: 4</t>
+          <t>L633: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -2219,21 +2083,17 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L374: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: She gave him none, but rose from her Youâ€™ve come back, then? she said,</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L737: isolated marker/symbol line :: 4</t>
+          <t>L583: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L805: isolated marker/symbol line :: 1</t>
+          <t>L656: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -2258,21 +2118,17 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L375: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: chair instrsled face. Just then "Yes, Iâ€™ve come back, Adelaide," he</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L763: isolated marker/symbol line :: A</t>
+          <t>L584: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L809: isolated marker/symbol line :: 00</t>
+          <t>L668: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2297,21 +2153,17 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L378: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: hall-firm, buoyant, elastic. for a moment. Youâ€™re not very strong.</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L777: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...$ 10, 000, 000</t>
+          <t>L609: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L811: isolated marker/symbol line :: 00</t>
+          <t>L805: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2336,21 +2188,17 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L380: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Mrs. Courtaine lifted one hand, and as youâ€™ve told me, and I hate to tax</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L814: isolated marker/symbol line :: 67</t>
+          <t>L610: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L813: isolated marker/symbol line :: 1</t>
+          <t>L809: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2375,21 +2223,17 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L385: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L818: isolated marker/symbol line :: -</t>
+          <t>L611: stray/suspicious non-ASCII glyph(s): U+5E7F CJK UNIFIED IDEOGRAPH-5E7F | isolated marker/symbol line :: 广</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L877: symbol-only separator/garbage line :: $10,000,000</t>
+          <t>L811: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2414,21 +2258,17 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L415: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L829: isolated marker/symbol line :: 4</t>
+          <t>L686: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L892: isolated marker/symbol line :: 1</t>
+          <t>L813: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2453,19 +2293,19 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L435: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: 2. â‚¬</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L830: isolated marker/symbol line :: E</t>
-        </is>
-      </c>
-      <c r="O37" s="1" t="inlineStr"/>
+          <t>L701: isolated marker/symbol line :: P</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>L877: symbol-only separator/garbage line :: $10,000,000</t>
+        </is>
+      </c>
       <c r="P37" s="1" t="inlineStr"/>
       <c r="Q37" s="1" t="inlineStr"/>
       <c r="R37" s="1" t="inlineStr"/>
@@ -2488,15 +2328,19 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L442: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
-      <c r="N38" s="1" t="inlineStr"/>
-      <c r="O38" s="1" t="inlineStr"/>
+      <c r="N38" s="1" t="inlineStr">
+        <is>
+          <t>L707: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>L892: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P38" s="1" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr"/>
       <c r="R38" s="1" t="inlineStr"/>
@@ -2519,14 +2363,14 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L494: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: than are the latter by constant feasts.â€”</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
-      <c r="N39" s="1" t="inlineStr"/>
+      <c r="N39" s="1" t="inlineStr">
+        <is>
+          <t>L737: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
       <c r="O39" s="1" t="inlineStr"/>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr"/>
@@ -2550,14 +2394,14 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L597: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
-      <c r="N40" s="1" t="inlineStr"/>
+      <c r="N40" s="1" t="inlineStr">
+        <is>
+          <t>L763: isolated marker/symbol line :: A</t>
+        </is>
+      </c>
       <c r="O40" s="1" t="inlineStr"/>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr"/>
@@ -2581,14 +2425,14 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L712: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ My son, my boy," she said, catching</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
-      <c r="N41" s="1" t="inlineStr"/>
+      <c r="N41" s="1" t="inlineStr">
+        <is>
+          <t>L777: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...$ 10, 000, 000</t>
+        </is>
+      </c>
       <c r="O41" s="1" t="inlineStr"/>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
@@ -2612,14 +2456,14 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L723: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Why, mother ?"â€”</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
-      <c r="N42" s="1" t="inlineStr"/>
+      <c r="N42" s="1" t="inlineStr">
+        <is>
+          <t>L814: isolated marker/symbol line :: 67</t>
+        </is>
+      </c>
       <c r="O42" s="1" t="inlineStr"/>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
@@ -2643,14 +2487,14 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L726: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: disobeyedâ€”I mean you've never refused</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
-      <c r="N43" s="1" t="inlineStr"/>
+      <c r="N43" s="1" t="inlineStr">
+        <is>
+          <t>L818: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="O43" s="1" t="inlineStr"/>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr"/>
@@ -2674,14 +2518,14 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L731: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: You want me to avoid seeing ?"â€”</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
-      <c r="N44" s="1" t="inlineStr"/>
+      <c r="N44" s="1" t="inlineStr">
+        <is>
+          <t>L829: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
       <c r="O44" s="1" t="inlineStr"/>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
@@ -2705,14 +2549,14 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L733: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: " Yes; thatâ€™s it; I want you to avoid</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
-      <c r="N45" s="1" t="inlineStr"/>
+      <c r="N45" s="1" t="inlineStr">
+        <is>
+          <t>L830: isolated marker/symbol line :: E</t>
+        </is>
+      </c>
       <c r="O45" s="1" t="inlineStr"/>
       <c r="P45" s="1" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr"/>
@@ -2725,161 +2569,6 @@
       <c r="X45" s="1" t="inlineStr"/>
       <c r="Y45" s="1" t="inlineStr"/>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr"/>
-      <c r="B46" s="1" t="inlineStr"/>
-      <c r="C46" s="1" t="inlineStr"/>
-      <c r="D46" s="1" t="inlineStr"/>
-      <c r="E46" s="1" t="inlineStr"/>
-      <c r="F46" s="1" t="inlineStr"/>
-      <c r="G46" s="1" t="inlineStr"/>
-      <c r="H46" s="1" t="inlineStr"/>
-      <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L736: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Carrollâ€™s face flushed suddenly and his</t>
-        </is>
-      </c>
-      <c r="L46" s="1" t="inlineStr"/>
-      <c r="M46" s="1" t="inlineStr"/>
-      <c r="N46" s="1" t="inlineStr"/>
-      <c r="O46" s="1" t="inlineStr"/>
-      <c r="P46" s="1" t="inlineStr"/>
-      <c r="Q46" s="1" t="inlineStr"/>
-      <c r="R46" s="1" t="inlineStr"/>
-      <c r="S46" s="1" t="inlineStr"/>
-      <c r="T46" s="1" t="inlineStr"/>
-      <c r="U46" s="1" t="inlineStr"/>
-      <c r="V46" s="1" t="inlineStr"/>
-      <c r="W46" s="1" t="inlineStr"/>
-      <c r="X46" s="1" t="inlineStr"/>
-      <c r="Y46" s="1" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr"/>
-      <c r="B47" s="1" t="inlineStr"/>
-      <c r="C47" s="1" t="inlineStr"/>
-      <c r="D47" s="1" t="inlineStr"/>
-      <c r="E47" s="1" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr"/>
-      <c r="G47" s="1" t="inlineStr"/>
-      <c r="H47" s="1" t="inlineStr"/>
-      <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L743: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: that it is. There "â€”and she pushed him</t>
-        </is>
-      </c>
-      <c r="L47" s="1" t="inlineStr"/>
-      <c r="M47" s="1" t="inlineStr"/>
-      <c r="N47" s="1" t="inlineStr"/>
-      <c r="O47" s="1" t="inlineStr"/>
-      <c r="P47" s="1" t="inlineStr"/>
-      <c r="Q47" s="1" t="inlineStr"/>
-      <c r="R47" s="1" t="inlineStr"/>
-      <c r="S47" s="1" t="inlineStr"/>
-      <c r="T47" s="1" t="inlineStr"/>
-      <c r="U47" s="1" t="inlineStr"/>
-      <c r="V47" s="1" t="inlineStr"/>
-      <c r="W47" s="1" t="inlineStr"/>
-      <c r="X47" s="1" t="inlineStr"/>
-      <c r="Y47" s="1" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr"/>
-      <c r="B48" s="1" t="inlineStr"/>
-      <c r="C48" s="1" t="inlineStr"/>
-      <c r="D48" s="1" t="inlineStr"/>
-      <c r="E48" s="1" t="inlineStr"/>
-      <c r="F48" s="1" t="inlineStr"/>
-      <c r="G48" s="1" t="inlineStr"/>
-      <c r="H48" s="1" t="inlineStr"/>
-      <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L818: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Dr. Pierceâ€™s Favorite Prescription is the best</t>
-        </is>
-      </c>
-      <c r="L48" s="1" t="inlineStr"/>
-      <c r="M48" s="1" t="inlineStr"/>
-      <c r="N48" s="1" t="inlineStr"/>
-      <c r="O48" s="1" t="inlineStr"/>
-      <c r="P48" s="1" t="inlineStr"/>
-      <c r="Q48" s="1" t="inlineStr"/>
-      <c r="R48" s="1" t="inlineStr"/>
-      <c r="S48" s="1" t="inlineStr"/>
-      <c r="T48" s="1" t="inlineStr"/>
-      <c r="U48" s="1" t="inlineStr"/>
-      <c r="V48" s="1" t="inlineStr"/>
-      <c r="W48" s="1" t="inlineStr"/>
-      <c r="X48" s="1" t="inlineStr"/>
-      <c r="Y48" s="1" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr"/>
-      <c r="B49" s="1" t="inlineStr"/>
-      <c r="C49" s="1" t="inlineStr"/>
-      <c r="D49" s="1" t="inlineStr"/>
-      <c r="E49" s="1" t="inlineStr"/>
-      <c r="F49" s="1" t="inlineStr"/>
-      <c r="G49" s="1" t="inlineStr"/>
-      <c r="H49" s="1" t="inlineStr"/>
-      <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L837: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: â€˜Prescription.â€™ I trust</t>
-        </is>
-      </c>
-      <c r="L49" s="1" t="inlineStr"/>
-      <c r="M49" s="1" t="inlineStr"/>
-      <c r="N49" s="1" t="inlineStr"/>
-      <c r="O49" s="1" t="inlineStr"/>
-      <c r="P49" s="1" t="inlineStr"/>
-      <c r="Q49" s="1" t="inlineStr"/>
-      <c r="R49" s="1" t="inlineStr"/>
-      <c r="S49" s="1" t="inlineStr"/>
-      <c r="T49" s="1" t="inlineStr"/>
-      <c r="U49" s="1" t="inlineStr"/>
-      <c r="V49" s="1" t="inlineStr"/>
-      <c r="W49" s="1" t="inlineStr"/>
-      <c r="X49" s="1" t="inlineStr"/>
-      <c r="Y49" s="1" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr"/>
-      <c r="B50" s="1" t="inlineStr"/>
-      <c r="C50" s="1" t="inlineStr"/>
-      <c r="D50" s="1" t="inlineStr"/>
-      <c r="E50" s="1" t="inlineStr"/>
-      <c r="F50" s="1" t="inlineStr"/>
-      <c r="G50" s="1" t="inlineStr"/>
-      <c r="H50" s="1" t="inlineStr"/>
-      <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L856: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: DUNNâ€™S</t>
-        </is>
-      </c>
-      <c r="L50" s="1" t="inlineStr"/>
-      <c r="M50" s="1" t="inlineStr"/>
-      <c r="N50" s="1" t="inlineStr"/>
-      <c r="O50" s="1" t="inlineStr"/>
-      <c r="P50" s="1" t="inlineStr"/>
-      <c r="Q50" s="1" t="inlineStr"/>
-      <c r="R50" s="1" t="inlineStr"/>
-      <c r="S50" s="1" t="inlineStr"/>
-      <c r="T50" s="1" t="inlineStr"/>
-      <c r="U50" s="1" t="inlineStr"/>
-      <c r="V50" s="1" t="inlineStr"/>
-      <c r="W50" s="1" t="inlineStr"/>
-      <c r="X50" s="1" t="inlineStr"/>
-      <c r="Y50" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
